--- a/templates/evidence-map-stopping-rule.xlsx
+++ b/templates/evidence-map-stopping-rule.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Map" sheetId="1" r:id="R97b8d4dbc3e448ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="2" r:id="Rafc90715245a41b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection Plan" sheetId="3" r:id="R947ff7aafe8e4fd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stopping Rule" sheetId="4" r:id="R50ea3dc140f7443a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="5" r:id="Rab4d0650868b48b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence Map" sheetId="1" r:id="Rcec3eff64d33418e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="2" r:id="R80667c921f3a48a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection Plan" sheetId="3" r:id="R0f75d47278bd44e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stopping Rule" sheetId="4" r:id="R32cbb4ca91ab45ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="5" r:id="Ra3e6e247de874a4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -179,7 +179,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1496,7 +1496,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>0.1 discussion draft, 2026-07-12</x:v>
+        <x:v>0.2 discussion draft, 2026-07-13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
